--- a/sampleprojects/TaxReturn/excel/states/ID.xlsx
+++ b/sampleprojects/TaxReturn/excel/states/ID.xlsx
@@ -83,7 +83,7 @@
     <t>MFJ/QSS: $30,000 std ded, 5.695%</t>
   </si>
   <si>
-    <t>set result.computed_state_taxable_income = the maximum of (result.agi - 30000.0) and 0.0; set result.computed_state_tax = result.computed_state_taxable_income * 0.05695</t>
+    <t>set result.computed_state_taxable_income = the maximum of (result.state_calc_agi - 30000.0) and 0.0; set result.computed_state_tax = result.computed_state_taxable_income * 0.05695</t>
   </si>
   <si>
     <t>X</t>
@@ -92,13 +92,13 @@
     <t>HOH: $22,500 std ded, 5.695%</t>
   </si>
   <si>
-    <t>set result.computed_state_taxable_income = the maximum of (result.agi - 22500.0) and 0.0; set result.computed_state_tax = result.computed_state_taxable_income * 0.05695</t>
+    <t>set result.computed_state_taxable_income = the maximum of (result.state_calc_agi - 22500.0) and 0.0; set result.computed_state_tax = result.computed_state_taxable_income * 0.05695</t>
   </si>
   <si>
     <t>Default (Single/MFS): $15,000 std ded, 5.695%</t>
   </si>
   <si>
-    <t>set result.computed_state_taxable_income = the maximum of (result.agi - 15000.0) and 0.0; set result.computed_state_tax = result.computed_state_taxable_income * 0.05695</t>
+    <t>set result.computed_state_taxable_income = the maximum of (result.state_calc_agi - 15000.0) and 0.0; set result.computed_state_tax = result.computed_state_taxable_income * 0.05695</t>
   </si>
   <si>
     <t>Policy:</t>

--- a/sampleprojects/TaxReturn/excel/states/ID.xlsx
+++ b/sampleprojects/TaxReturn/excel/states/ID.xlsx
@@ -8,14 +8,15 @@
   </bookViews>
   <sheets>
     <sheet name="ID Tax" sheetId="2" r:id="rId4"/>
-    <sheet name="EDD" sheetId="3" r:id="rId6"/>
+    <sheet name="ID Retirement Benefits Deductio" sheetId="3" r:id="rId6"/>
+    <sheet name="EDD" sheetId="4" r:id="rId7"/>
   </sheets>
   <calcPr calcId="122211"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="89">
   <si>
     <t>DT: ID Tax</t>
   </si>
@@ -44,7 +45,7 @@
     <t/>
   </si>
   <si>
-    <t>set result.computed_state_tax = 0; set result.computed_state_taxable_income = 0; add "  Idaho Tax Calculation (top marginal 5.695%)" to job.audit_trail</t>
+    <t>set result.computed_state_tax = 0; set result.computed_state_taxable_income = 0; set result.id_military_retirement_exemption = 0.0; perform ID_Retirement_Benefits_Deduction; add "  Idaho Tax Calculation (Form 40, 2025) - 5.3% of taxable income above the zero bracket" to job.audit_trail</t>
   </si>
   <si>
     <t>CONDITIONS: COMMENTS</t>
@@ -80,25 +81,25 @@
     <t>DSL: ACTIONS</t>
   </si>
   <si>
-    <t>MFJ/QSS: $30,000 std ded, 5.695%</t>
-  </si>
-  <si>
-    <t>set result.computed_state_taxable_income = the maximum of (result.state_calc_agi - 30000.0) and 0.0; set result.computed_state_tax = result.computed_state_taxable_income * 0.05695</t>
+    <t>MFJ/QSS: Form 39R line 8a cap $72,324 less Social Security; Form 40 line 16 federal deduction; line 20 worksheet: subtract $9,622, multiply by 5.3%</t>
+  </si>
+  <si>
+    <t>set result.id_military_retirement_exemption = the maximum of ((the minimum of result.id_military_retirement_exemption and id_retirement_benefits_cap_joint) - result.total_social_security) and 0.0; set result.computed_state_taxable_income = the maximum of (result.state_calc_agi - result.id_military_retirement_exemption - result.total_deduction) and 0.0; set result.computed_state_tax = (the maximum of (result.computed_state_taxable_income - id_zero_bracket_joint) and 0.0) * id_tax_rate; add "  ID Form 39R line 8 retirement benefits deduction $" + result.id_military_retirement_exemption + "; taxable income $" + result.computed_state_taxable_income + "; tax $" + result.computed_state_tax to job.audit_trail</t>
   </si>
   <si>
     <t>X</t>
   </si>
   <si>
-    <t>HOH: $22,500 std ded, 5.695%</t>
-  </si>
-  <si>
-    <t>set result.computed_state_taxable_income = the maximum of (result.state_calc_agi - 22500.0) and 0.0; set result.computed_state_tax = result.computed_state_taxable_income * 0.05695</t>
-  </si>
-  <si>
-    <t>Default (Single/MFS): $15,000 std ded, 5.695%</t>
-  </si>
-  <si>
-    <t>set result.computed_state_taxable_income = the maximum of (result.state_calc_agi - 15000.0) and 0.0; set result.computed_state_tax = result.computed_state_taxable_income * 0.05695</t>
+    <t>HOH: single cap on Form 39R line 8a; the head-of-household zero bracket is the joint figure, $9,622; 5.3%</t>
+  </si>
+  <si>
+    <t>set result.id_military_retirement_exemption = the maximum of ((the minimum of result.id_military_retirement_exemption and id_retirement_benefits_cap_single) - result.total_social_security) and 0.0; set result.computed_state_taxable_income = the maximum of (result.state_calc_agi - result.id_military_retirement_exemption - result.total_deduction) and 0.0; set result.computed_state_tax = (the maximum of (result.computed_state_taxable_income - id_zero_bracket_joint) and 0.0) * id_tax_rate; add "  ID Form 39R line 8 retirement benefits deduction $" + result.id_military_retirement_exemption + "; taxable income $" + result.computed_state_taxable_income + "; tax $" + result.computed_state_tax to job.audit_trail</t>
+  </si>
+  <si>
+    <t>Single/MFS: Form 39R line 8a cap $48,216 less Social Security; Form 40 line 16 federal deduction; line 20 worksheet: subtract $4,811, multiply by 5.3%</t>
+  </si>
+  <si>
+    <t>set result.id_military_retirement_exemption = the maximum of ((the minimum of result.id_military_retirement_exemption and id_retirement_benefits_cap_single) - result.total_social_security) and 0.0; set result.computed_state_taxable_income = the maximum of (result.state_calc_agi - result.id_military_retirement_exemption - result.total_deduction) and 0.0; set result.computed_state_tax = (the maximum of (result.computed_state_taxable_income - id_zero_bracket_single) and 0.0) * id_tax_rate; add "  ID Form 39R line 8 retirement benefits deduction $" + result.id_military_retirement_exemption + "; taxable income $" + result.computed_state_taxable_income + "; tax $" + result.computed_state_tax to job.audit_trail</t>
   </si>
   <si>
     <t>Policy:</t>
@@ -107,13 +108,58 @@
     <t>Policy Statements</t>
   </si>
   <si>
-    <t>ID MFJ: 5.695% x max(AGI - $30,000, 0) per Idaho Code § 63-3024</t>
-  </si>
-  <si>
-    <t>ID HOH: 5.695% x max(AGI - $22,500, 0) per Idaho Code § 63-3024</t>
-  </si>
-  <si>
-    <t>ID Single/MFS: 5.695% x max(AGI - $15,000, 0) per Idaho Code § 63-3024</t>
+    <t>Idaho MFJ/QSS (2025 Form 40): taxable income is federal AGI less Form 39R subtractions (the retirement benefits deduction for military retired pay, capped at $72,324 less Social Security) less the federal deduction (line 16); tax is 5.3% of taxable income over the $9,622 zero bracket (line 20 worksheet; HB 40).</t>
+  </si>
+  <si>
+    <t>Idaho HOH: as MFJ, with the single $48,216 cap on the retirement benefits deduction.</t>
+  </si>
+  <si>
+    <t>Idaho Single/MFS (2025 Form 40): federal AGI less the retirement benefits deduction (Form 39R Part B line 8, cap $48,216 less Social Security) less the federal deduction; 5.3% of taxable income over the $4,811 zero bracket. The refundable grocery credit and the $10 permanent building fund tax are not part of the income tax figure.</t>
+  </si>
+  <si>
+    <t>DT: ID Retirement Benefits Deduction</t>
+  </si>
+  <si>
+    <t xml:space="preserve">COMMENTS: </t>
+  </si>
+  <si>
+    <t>TABLE_NUMBER: 51613</t>
+  </si>
+  <si>
+    <t>for all taxpayers</t>
+  </si>
+  <si>
+    <t>The taxpayer has military retired pay (Form 39R Part B line 8e qualifying benefits)</t>
+  </si>
+  <si>
+    <t>taxpayer.military_retirement_pay &gt; 0</t>
+  </si>
+  <si>
+    <t>62 or older qualifies outright (Idaho Code 63-3022A(1)(b)(ii))</t>
+  </si>
+  <si>
+    <t>job.tax_year - (get yearof taxpayer.date_of_birth) &gt;= 62</t>
+  </si>
+  <si>
+    <t>Under 62: qualifies when employed during the year with enough income to have to file a federal return (63-3022A(1)(b)(iii)); wages stand in for that test</t>
+  </si>
+  <si>
+    <t>taxpayer.w2_wages &gt; 0</t>
+  </si>
+  <si>
+    <t>Form 39R Part B line 8e: qualifying retirement benefits of a retired service member; capped on line 8a-8f in ID_Tax</t>
+  </si>
+  <si>
+    <t>add taxpayer.military_retirement_pay to result.id_military_retirement_exemption</t>
+  </si>
+  <si>
+    <t>62 or older: the military retired pay is a qualifying retirement benefit for the Idaho retirement benefits deduction (Form 39R Part B line 8; Idaho Code 63-3022A; 2025 Form 39R instructions p. 31).</t>
+  </si>
+  <si>
+    <t>Under 62 and employed: the pay qualifies for the retirement benefits deduction (63-3022A(1)(b)(iii)). The disabled-at-any-age test has no input in the data model.</t>
+  </si>
+  <si>
+    <t>Under 62 and not employed, or no military retired pay: no deduction.</t>
   </si>
   <si>
     <t>EDD: EDD</t>
@@ -161,7 +207,7 @@
     <t>result</t>
   </si>
   <si>
-    <t>(3 attributes)</t>
+    <t>(8 attributes)</t>
   </si>
   <si>
     <t>id_military_age_requirement</t>
@@ -176,7 +222,7 @@
     <t>r</t>
   </si>
   <si>
-    <t>ID minimum age for full military retirement exemption (62)</t>
+    <t>Idaho retirement benefits deduction for retired service members: age 62 or older qualifies outright; under 62 qualifies only when employed during the year with enough earned income to have to file a federal return; disabled qualifies at any age (Idaho Code 63-3022A(1)(b); 2025 Form 39R instructions, line 8e). Military retired pay is not exempt without one of these tests.</t>
   </si>
   <si>
     <t>id_military_retirement_exemption</t>
@@ -185,13 +231,58 @@
     <t>0.0</t>
   </si>
   <si>
-    <t>ID military retirement exemption (computed - full if qualified)</t>
+    <t>Idaho retirement benefits deduction for military retired pay (computed): the qualifying pay (ID_Retirement_Benefits_Deduction, per taxpayer), capped at the filing-status maximum less Social Security received (Form 39R Part B line 8f -&gt; line 24 -&gt; Form 40 line 10) (#1330).</t>
   </si>
   <si>
     <t>id_military_retirement_taxable</t>
   </si>
   <si>
     <t>ID taxable military retirement after exemption (computed)</t>
+  </si>
+  <si>
+    <t>id_retirement_benefits_cap_joint</t>
+  </si>
+  <si>
+    <t>72324.0</t>
+  </si>
+  <si>
+    <t>Idaho retirement benefits deduction maximum, married filing jointly: $72,324 for 2025 (Form 39R Part B line 8a; 2025 Form 39R instructions p. 31).</t>
+  </si>
+  <si>
+    <t>id_retirement_benefits_cap_single</t>
+  </si>
+  <si>
+    <t>48216.0</t>
+  </si>
+  <si>
+    <t>Idaho retirement benefits deduction maximum, single: $48,216 for 2025, reduced by Social Security and Railroad Retirement benefits received (Form 39R Part B line 8a; Idaho Code 63-3022A; 2025 Form 39R instructions p. 31).</t>
+  </si>
+  <si>
+    <t>id_tax_rate</t>
+  </si>
+  <si>
+    <t>0.053</t>
+  </si>
+  <si>
+    <t>Idaho individual income tax rate 5.3% effective January 1, 2025 (HB 40; 2025 Form 40 instructions, line 20 worksheet step 4). Was 5.695% for 2024.</t>
+  </si>
+  <si>
+    <t>id_zero_bracket_joint</t>
+  </si>
+  <si>
+    <t>9622.0</t>
+  </si>
+  <si>
+    <t>Idaho taxable income not taxed, married filing jointly, surviving spouse or head of household: $9,622 for 2025, twice the single figure as in prior years (2024: $4,673 single, $9,346 joint). The 2025 joint figure was not read from the Form 40 worksheet directly; confirm when a joint Idaho scenario is written.</t>
+  </si>
+  <si>
+    <t>id_zero_bracket_single</t>
+  </si>
+  <si>
+    <t>4811.0</t>
+  </si>
+  <si>
+    <t>Idaho taxable income not taxed, single or married filing separately: $4,811 for 2025 (Form 40 instructions, line 20 worksheet step 2).</t>
   </si>
 </sst>
 </file>
@@ -1479,6 +1570,786 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <dimension ref="A1"/>
   <cols>
+    <col customWidth="true" max="1" min="1" width="20"/>
+    <col customWidth="true" max="3" min="2" width="40"/>
+    <col customWidth="true" max="19" min="4" width="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="B1" s="2"/>
+      <c r="C1" s="2"/>
+      <c r="D1" s="2"/>
+      <c r="E1" s="2"/>
+      <c r="F1" s="2"/>
+      <c r="G1" s="2"/>
+      <c r="H1" s="2"/>
+      <c r="I1" s="2"/>
+      <c r="J1" s="2"/>
+      <c r="K1" s="2"/>
+      <c r="L1" s="2"/>
+      <c r="M1" s="2"/>
+      <c r="N1" s="2"/>
+      <c r="O1" s="2"/>
+      <c r="P1" s="2"/>
+      <c r="Q1" s="2"/>
+      <c r="R1" s="2"/>
+      <c r="S1" s="2"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="3"/>
+      <c r="C2" s="3"/>
+      <c r="D2" s="3"/>
+      <c r="E2" s="3"/>
+      <c r="F2" s="3"/>
+      <c r="G2" s="3"/>
+      <c r="H2" s="3"/>
+      <c r="I2" s="3"/>
+      <c r="J2" s="3"/>
+      <c r="K2" s="3"/>
+      <c r="L2" s="3"/>
+      <c r="M2" s="3"/>
+      <c r="N2" s="3"/>
+      <c r="O2" s="3"/>
+      <c r="P2" s="3"/>
+      <c r="Q2" s="3"/>
+      <c r="R2" s="3"/>
+      <c r="S2" s="3"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="B3" s="2"/>
+      <c r="C3" s="2"/>
+      <c r="D3" s="2"/>
+      <c r="E3" s="2"/>
+      <c r="F3" s="2"/>
+      <c r="G3" s="2"/>
+      <c r="H3" s="2"/>
+      <c r="I3" s="2"/>
+      <c r="J3" s="2"/>
+      <c r="K3" s="2"/>
+      <c r="L3" s="2"/>
+      <c r="M3" s="2"/>
+      <c r="N3" s="2"/>
+      <c r="O3" s="2"/>
+      <c r="P3" s="2"/>
+      <c r="Q3" s="2"/>
+      <c r="R3" s="2"/>
+      <c r="S3" s="2"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="B4" s="2"/>
+      <c r="C4" s="2"/>
+      <c r="D4" s="2"/>
+      <c r="E4" s="2"/>
+      <c r="F4" s="2"/>
+      <c r="G4" s="2"/>
+      <c r="H4" s="2"/>
+      <c r="I4" s="2"/>
+      <c r="J4" s="2"/>
+      <c r="K4" s="2"/>
+      <c r="L4" s="2"/>
+      <c r="M4" s="2"/>
+      <c r="N4" s="2"/>
+      <c r="O4" s="2"/>
+      <c r="P4" s="2"/>
+      <c r="Q4" s="2"/>
+      <c r="R4" s="2"/>
+      <c r="S4" s="2"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B6" s="1"/>
+      <c r="C6" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D6" s="1"/>
+      <c r="E6" s="1"/>
+      <c r="F6" s="1"/>
+      <c r="G6" s="1"/>
+      <c r="H6" s="1"/>
+      <c r="I6" s="1"/>
+      <c r="J6" s="1"/>
+      <c r="K6" s="1"/>
+      <c r="L6" s="1"/>
+      <c r="M6" s="1"/>
+      <c r="N6" s="1"/>
+      <c r="O6" s="1"/>
+      <c r="P6" s="1"/>
+      <c r="Q6" s="1"/>
+      <c r="R6" s="1"/>
+      <c r="S6" s="1"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="5">
+        <v>1</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="D7" s="3"/>
+      <c r="E7" s="3"/>
+      <c r="F7" s="3"/>
+      <c r="G7" s="3"/>
+      <c r="H7" s="3"/>
+      <c r="I7" s="3"/>
+      <c r="J7" s="3"/>
+      <c r="K7" s="3"/>
+      <c r="L7" s="3"/>
+      <c r="M7" s="3"/>
+      <c r="N7" s="3"/>
+      <c r="O7" s="3"/>
+      <c r="P7" s="3"/>
+      <c r="Q7" s="3"/>
+      <c r="R7" s="3"/>
+      <c r="S7" s="3"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B9" s="1"/>
+      <c r="C9" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D9" s="1"/>
+      <c r="E9" s="1"/>
+      <c r="F9" s="1"/>
+      <c r="G9" s="1"/>
+      <c r="H9" s="1"/>
+      <c r="I9" s="1"/>
+      <c r="J9" s="1"/>
+      <c r="K9" s="1"/>
+      <c r="L9" s="1"/>
+      <c r="M9" s="1"/>
+      <c r="N9" s="1"/>
+      <c r="O9" s="1"/>
+      <c r="P9" s="1"/>
+      <c r="Q9" s="1"/>
+      <c r="R9" s="1"/>
+      <c r="S9" s="1"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B11" s="1"/>
+      <c r="C11" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D11" s="1">
+        <v>1</v>
+      </c>
+      <c r="E11" s="1">
+        <v>2</v>
+      </c>
+      <c r="F11" s="1">
+        <v>3</v>
+      </c>
+      <c r="G11" s="1">
+        <v>4</v>
+      </c>
+      <c r="H11" s="1">
+        <v>5</v>
+      </c>
+      <c r="I11" s="1">
+        <v>6</v>
+      </c>
+      <c r="J11" s="1">
+        <v>7</v>
+      </c>
+      <c r="K11" s="1">
+        <v>8</v>
+      </c>
+      <c r="L11" s="1">
+        <v>9</v>
+      </c>
+      <c r="M11" s="1">
+        <v>10</v>
+      </c>
+      <c r="N11" s="1">
+        <v>11</v>
+      </c>
+      <c r="O11" s="1">
+        <v>12</v>
+      </c>
+      <c r="P11" s="1">
+        <v>13</v>
+      </c>
+      <c r="Q11" s="1">
+        <v>14</v>
+      </c>
+      <c r="R11" s="1">
+        <v>15</v>
+      </c>
+      <c r="S11" s="1">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="5">
+        <v>1</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="G12" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="I12" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="J12" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="K12" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="L12" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="M12" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="N12" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="O12" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="P12" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q12" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="R12" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="S12" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="5">
+        <v>2</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="G13" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="I13" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="J13" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="K13" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="L13" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="M13" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="N13" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="O13" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="P13" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q13" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="R13" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="S13" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="5">
+        <v>3</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="F14" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="G14" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H14" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="I14" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="J14" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="K14" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="L14" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="M14" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="N14" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="O14" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="P14" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q14" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="R14" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="S14" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B16" s="1"/>
+      <c r="C16" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="D16" s="4">
+        <v>1</v>
+      </c>
+      <c r="E16" s="4">
+        <v>2</v>
+      </c>
+      <c r="F16" s="4">
+        <v>3</v>
+      </c>
+      <c r="G16" s="4">
+        <v>4</v>
+      </c>
+      <c r="H16" s="4">
+        <v>5</v>
+      </c>
+      <c r="I16" s="4">
+        <v>6</v>
+      </c>
+      <c r="J16" s="4">
+        <v>7</v>
+      </c>
+      <c r="K16" s="4">
+        <v>8</v>
+      </c>
+      <c r="L16" s="4">
+        <v>9</v>
+      </c>
+      <c r="M16" s="4">
+        <v>10</v>
+      </c>
+      <c r="N16" s="4">
+        <v>11</v>
+      </c>
+      <c r="O16" s="4">
+        <v>12</v>
+      </c>
+      <c r="P16" s="4">
+        <v>13</v>
+      </c>
+      <c r="Q16" s="4">
+        <v>14</v>
+      </c>
+      <c r="R16" s="4">
+        <v>15</v>
+      </c>
+      <c r="S16" s="4">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="5">
+        <v>1</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="F17" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="G17" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H17" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="I17" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="J17" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="K17" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="L17" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="M17" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="N17" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="O17" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="P17" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q17" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="R17" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="S17" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B19" s="1"/>
+      <c r="C19" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D19" s="1">
+        <v>1</v>
+      </c>
+      <c r="E19" s="1">
+        <v>2</v>
+      </c>
+      <c r="F19" s="1">
+        <v>3</v>
+      </c>
+      <c r="G19" s="1">
+        <v>4</v>
+      </c>
+      <c r="H19" s="1">
+        <v>5</v>
+      </c>
+      <c r="I19" s="1">
+        <v>6</v>
+      </c>
+      <c r="J19" s="1">
+        <v>7</v>
+      </c>
+      <c r="K19" s="1">
+        <v>8</v>
+      </c>
+      <c r="L19" s="1">
+        <v>9</v>
+      </c>
+      <c r="M19" s="1">
+        <v>10</v>
+      </c>
+      <c r="N19" s="1">
+        <v>11</v>
+      </c>
+      <c r="O19" s="1">
+        <v>12</v>
+      </c>
+      <c r="P19" s="1">
+        <v>13</v>
+      </c>
+      <c r="Q19" s="1">
+        <v>14</v>
+      </c>
+      <c r="R19" s="1">
+        <v>15</v>
+      </c>
+      <c r="S19" s="1">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="5">
+        <v>1</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F20" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="G20" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H20" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="I20" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="J20" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="K20" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="L20" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="M20" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="N20" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="O20" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="P20" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q20" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="R20" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="S20" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="5">
+        <v>2</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F21" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="G21" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H21" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="I21" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="J21" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="K21" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="L21" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="M21" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="N21" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="O21" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="P21" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q21" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="R21" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="S21" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="5">
+        <v>3</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F22" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="G22" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H22" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="I22" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="J22" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="K22" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="L22" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="M22" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="N22" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="O22" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="P22" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q22" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="R22" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="S22" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="12">
+    <mergeCell ref="A1:S1"/>
+    <mergeCell ref="A2:S2"/>
+    <mergeCell ref="A3:S3"/>
+    <mergeCell ref="A4:S4"/>
+    <mergeCell ref="A6:B6"/>
+    <mergeCell ref="C6:S6"/>
+    <mergeCell ref="C7:S7"/>
+    <mergeCell ref="A9:B9"/>
+    <mergeCell ref="C9:S9"/>
+    <mergeCell ref="A11:B11"/>
+    <mergeCell ref="A16:B16"/>
+    <mergeCell ref="A19:B19"/>
+  </mergeCells>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1"/>
+  <cols>
     <col customWidth="true" max="1" min="1" width="18"/>
     <col customWidth="true" max="2" min="2" width="25"/>
     <col customWidth="true" max="3" min="3" width="10"/>
@@ -1495,56 +2366,56 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>33</v>
+        <v>48</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
-        <v>34</v>
+        <v>49</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>35</v>
+        <v>50</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>36</v>
+        <v>51</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>37</v>
+        <v>52</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>38</v>
+        <v>53</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>39</v>
+        <v>54</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>41</v>
+        <v>56</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>42</v>
+        <v>57</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>43</v>
+        <v>58</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>44</v>
+        <v>59</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="M2" s="1" t="s">
-        <v>46</v>
+        <v>61</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="6" t="s">
-        <v>47</v>
+        <v>62</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>48</v>
+        <v>63</v>
       </c>
       <c r="C3" s="6"/>
       <c r="D3" s="6"/>
@@ -1563,25 +2434,25 @@
         <v>8</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>49</v>
+        <v>64</v>
       </c>
       <c r="C4" s="11" t="s">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="D4" s="7" t="s">
         <v>8</v>
       </c>
       <c r="E4" s="7" t="s">
-        <v>51</v>
+        <v>66</v>
       </c>
       <c r="F4" s="7" t="s">
         <v>8</v>
       </c>
       <c r="G4" s="7" t="s">
-        <v>52</v>
+        <v>67</v>
       </c>
       <c r="H4" s="16" t="s">
-        <v>53</v>
+        <v>68</v>
       </c>
       <c r="I4" s="7" t="s">
         <v>8</v>
@@ -1604,25 +2475,25 @@
         <v>8</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>54</v>
+        <v>69</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="D5" s="8" t="s">
         <v>8</v>
       </c>
       <c r="E5" s="8" t="s">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="F5" s="8" t="s">
         <v>8</v>
       </c>
       <c r="G5" s="8" t="s">
-        <v>52</v>
+        <v>67</v>
       </c>
       <c r="H5" s="16" t="s">
-        <v>56</v>
+        <v>71</v>
       </c>
       <c r="I5" s="8" t="s">
         <v>8</v>
@@ -1645,25 +2516,25 @@
         <v>8</v>
       </c>
       <c r="B6" s="9" t="s">
-        <v>57</v>
+        <v>72</v>
       </c>
       <c r="C6" s="11" t="s">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="D6" s="7" t="s">
         <v>8</v>
       </c>
       <c r="E6" s="7" t="s">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="F6" s="7" t="s">
         <v>8</v>
       </c>
       <c r="G6" s="7" t="s">
-        <v>52</v>
+        <v>67</v>
       </c>
       <c r="H6" s="16" t="s">
-        <v>58</v>
+        <v>73</v>
       </c>
       <c r="I6" s="7" t="s">
         <v>8</v>
@@ -1678,6 +2549,211 @@
         <v>8</v>
       </c>
       <c r="M6" s="7" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="B7" s="9" t="s">
+        <v>74</v>
+      </c>
+      <c r="C7" s="11" t="s">
+        <v>65</v>
+      </c>
+      <c r="D7" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E7" s="8" t="s">
+        <v>75</v>
+      </c>
+      <c r="F7" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="G7" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="H7" s="16" t="s">
+        <v>76</v>
+      </c>
+      <c r="I7" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="J7" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="K7" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="L7" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="M7" s="8" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="B8" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="C8" s="11" t="s">
+        <v>65</v>
+      </c>
+      <c r="D8" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E8" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="F8" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="G8" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="H8" s="16" t="s">
+        <v>79</v>
+      </c>
+      <c r="I8" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="J8" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="K8" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="L8" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="M8" s="7" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="B9" s="9" t="s">
+        <v>80</v>
+      </c>
+      <c r="C9" s="11" t="s">
+        <v>65</v>
+      </c>
+      <c r="D9" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E9" s="8" t="s">
+        <v>81</v>
+      </c>
+      <c r="F9" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="G9" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="H9" s="16" t="s">
+        <v>82</v>
+      </c>
+      <c r="I9" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="J9" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="K9" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="L9" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="M9" s="8" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="B10" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="C10" s="11" t="s">
+        <v>65</v>
+      </c>
+      <c r="D10" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E10" s="7" t="s">
+        <v>84</v>
+      </c>
+      <c r="F10" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="G10" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="H10" s="16" t="s">
+        <v>85</v>
+      </c>
+      <c r="I10" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="J10" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="K10" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="L10" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="M10" s="7" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="B11" s="9" t="s">
+        <v>86</v>
+      </c>
+      <c r="C11" s="11" t="s">
+        <v>65</v>
+      </c>
+      <c r="D11" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E11" s="8" t="s">
+        <v>87</v>
+      </c>
+      <c r="F11" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="G11" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="H11" s="16" t="s">
+        <v>88</v>
+      </c>
+      <c r="I11" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="J11" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="K11" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="L11" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="M11" s="8" t="s">
         <v>8</v>
       </c>
     </row>

--- a/sampleprojects/TaxReturn/excel/states/ID.xlsx
+++ b/sampleprojects/TaxReturn/excel/states/ID.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="92">
   <si>
     <t>DT: ID Tax</t>
   </si>
@@ -81,25 +81,25 @@
     <t>DSL: ACTIONS</t>
   </si>
   <si>
-    <t>MFJ/QSS: Form 39R line 8a cap $72,324 less Social Security; Form 40 line 16 federal deduction; line 20 worksheet: subtract $9,622, multiply by 5.3%</t>
-  </si>
-  <si>
-    <t>set result.id_military_retirement_exemption = the maximum of ((the minimum of result.id_military_retirement_exemption and id_retirement_benefits_cap_joint) - result.total_social_security) and 0.0; set result.computed_state_taxable_income = the maximum of (result.state_calc_agi - result.id_military_retirement_exemption - result.total_deduction) and 0.0; set result.computed_state_tax = (the maximum of (result.computed_state_taxable_income - id_zero_bracket_joint) and 0.0) * id_tax_rate; add "  ID Form 39R line 8 retirement benefits deduction $" + result.id_military_retirement_exemption + "; taxable income $" + result.computed_state_taxable_income + "; tax $" + result.computed_state_tax to job.audit_trail</t>
+    <t>MFJ/QSS: Form 39R line 8d = the $72,324 cap less Social Security; 8f = the smaller of 8d and the benefits; Form 40 line 16 federal deduction; line 20 worksheet: subtract $9,622, multiply by 5.3%</t>
+  </si>
+  <si>
+    <t>set result.id_military_retirement_exemption = the minimum of result.id_military_retirement_exemption and (the maximum of (id_retirement_benefits_cap_joint - result.total_social_security) and 0.0); set result.computed_state_taxable_income = the maximum of (result.state_calc_agi - result.id_military_retirement_exemption - result.total_deduction) and 0.0; set result.computed_state_tax = (the maximum of (result.computed_state_taxable_income - id_zero_bracket_joint) and 0.0) * id_tax_rate; add "  ID Form 39R line 8 retirement benefits deduction $" + result.id_military_retirement_exemption + "; taxable income $" + result.computed_state_taxable_income + "; tax $" + result.computed_state_tax to job.audit_trail</t>
   </si>
   <si>
     <t>X</t>
   </si>
   <si>
-    <t>HOH: single cap on Form 39R line 8a; the head-of-household zero bracket is the joint figure, $9,622; 5.3%</t>
-  </si>
-  <si>
-    <t>set result.id_military_retirement_exemption = the maximum of ((the minimum of result.id_military_retirement_exemption and id_retirement_benefits_cap_single) - result.total_social_security) and 0.0; set result.computed_state_taxable_income = the maximum of (result.state_calc_agi - result.id_military_retirement_exemption - result.total_deduction) and 0.0; set result.computed_state_tax = (the maximum of (result.computed_state_taxable_income - id_zero_bracket_joint) and 0.0) * id_tax_rate; add "  ID Form 39R line 8 retirement benefits deduction $" + result.id_military_retirement_exemption + "; taxable income $" + result.computed_state_taxable_income + "; tax $" + result.computed_state_tax to job.audit_trail</t>
-  </si>
-  <si>
-    <t>Single/MFS: Form 39R line 8a cap $48,216 less Social Security; Form 40 line 16 federal deduction; line 20 worksheet: subtract $4,811, multiply by 5.3%</t>
-  </si>
-  <si>
-    <t>set result.id_military_retirement_exemption = the maximum of ((the minimum of result.id_military_retirement_exemption and id_retirement_benefits_cap_single) - result.total_social_security) and 0.0; set result.computed_state_taxable_income = the maximum of (result.state_calc_agi - result.id_military_retirement_exemption - result.total_deduction) and 0.0; set result.computed_state_tax = (the maximum of (result.computed_state_taxable_income - id_zero_bracket_single) and 0.0) * id_tax_rate; add "  ID Form 39R line 8 retirement benefits deduction $" + result.id_military_retirement_exemption + "; taxable income $" + result.computed_state_taxable_income + "; tax $" + result.computed_state_tax to job.audit_trail</t>
+    <t>HOH: Form 39R line 8d = the single $48,216 cap less Social Security; 8f = the smaller of 8d and the benefits; the head-of-household zero bracket is the joint figure, $9,622; 5.3%</t>
+  </si>
+  <si>
+    <t>set result.id_military_retirement_exemption = the minimum of result.id_military_retirement_exemption and (the maximum of (id_retirement_benefits_cap_single - result.total_social_security) and 0.0); set result.computed_state_taxable_income = the maximum of (result.state_calc_agi - result.id_military_retirement_exemption - result.total_deduction) and 0.0; set result.computed_state_tax = (the maximum of (result.computed_state_taxable_income - id_zero_bracket_joint) and 0.0) * id_tax_rate; add "  ID Form 39R line 8 retirement benefits deduction $" + result.id_military_retirement_exemption + "; taxable income $" + result.computed_state_taxable_income + "; tax $" + result.computed_state_tax to job.audit_trail</t>
+  </si>
+  <si>
+    <t>Single/MFS: Form 39R line 8d = the $48,216 cap less Social Security; 8f = the smaller of 8d and the benefits; Form 40 line 16 federal deduction; line 20 worksheet: subtract $4,811, multiply by 5.3%</t>
+  </si>
+  <si>
+    <t>set result.id_military_retirement_exemption = the minimum of result.id_military_retirement_exemption and (the maximum of (id_retirement_benefits_cap_single - result.total_social_security) and 0.0); set result.computed_state_taxable_income = the maximum of (result.state_calc_agi - result.id_military_retirement_exemption - result.total_deduction) and 0.0; set result.computed_state_tax = (the maximum of (result.computed_state_taxable_income - id_zero_bracket_single) and 0.0) * id_tax_rate; add "  ID Form 39R line 8 retirement benefits deduction $" + result.id_military_retirement_exemption + "; taxable income $" + result.computed_state_taxable_income + "; tax $" + result.computed_state_tax to job.audit_trail</t>
   </si>
   <si>
     <t>Policy:</t>
@@ -108,13 +108,13 @@
     <t>Policy Statements</t>
   </si>
   <si>
-    <t>Idaho MFJ/QSS (2025 Form 40): taxable income is federal AGI less Form 39R subtractions (the retirement benefits deduction for military retired pay, capped at $72,324 less Social Security) less the federal deduction (line 16); tax is 5.3% of taxable income over the $9,622 zero bracket (line 20 worksheet; HB 40).</t>
-  </si>
-  <si>
-    <t>Idaho HOH: as MFJ, with the single $48,216 cap on the retirement benefits deduction.</t>
-  </si>
-  <si>
-    <t>Idaho Single/MFS (2025 Form 40): federal AGI less the retirement benefits deduction (Form 39R Part B line 8, cap $48,216 less Social Security) less the federal deduction; 5.3% of taxable income over the $4,811 zero bracket. The refundable grocery credit and the $10 permanent building fund tax are not part of the income tax figure.</t>
+    <t>Idaho MFJ/QSS (2025 Form 40): taxable income is federal AGI less Form 39R subtractions (the retirement benefits deduction for military retired pay: line 8d = the $72,324 cap less Social Security, line 8f = the smaller of 8d and the benefits) less the federal deduction (line 16); tax is 5.3% of taxable income over the $9,622 zero bracket (line 20 worksheet; HB 40).</t>
+  </si>
+  <si>
+    <t>Idaho HOH: as MFJ, with the single $48,216 cap on Form 39R line 8a (8d = cap less Social Security; 8f = the smaller of 8d and the benefits).</t>
+  </si>
+  <si>
+    <t>Idaho Single/MFS (2025 Form 40): federal AGI less the retirement benefits deduction (Form 39R Part B line 8: 8d = the $48,216 cap less Social Security, 8f = the smaller of 8d and the benefits) less the federal deduction; 5.3% of taxable income over the $4,811 zero bracket. The refundable grocery credit and the $10 permanent building fund tax are not part of the income tax figure.</t>
   </si>
   <si>
     <t>DT: ID Retirement Benefits Deduction</t>
@@ -147,6 +147,12 @@
     <t>taxpayer.w2_wages &gt; 0</t>
   </si>
   <si>
+    <t>Full-year resident entry only. A part-year or nonresident entry's income is built from the income entities, so the pension is not in it, and 4 U.S.C. 114 bars a state from taxing a nonresident's retirement income (#1330 review).</t>
+  </si>
+  <si>
+    <t>result.state_calc_resident_status is equal to "full_year"</t>
+  </si>
+  <si>
     <t>Form 39R Part B line 8e: qualifying retirement benefits of a retired service member; capped on line 8a-8f in ID_Tax</t>
   </si>
   <si>
@@ -162,6 +168,9 @@
     <t>Under 62 and not employed, or no military retired pay: no deduction.</t>
   </si>
   <si>
+    <t>Not a full-year resident entry: the pension is not in this entry's sourced income (the roster builds it from the income entities) and 4 U.S.C. 114 bars taxing a nonresident's retirement income, so nothing is subtracted.</t>
+  </si>
+  <si>
     <t>EDD: EDD</t>
   </si>
   <si>
@@ -246,7 +255,7 @@
     <t>72324.0</t>
   </si>
   <si>
-    <t>Idaho retirement benefits deduction maximum, married filing jointly: $72,324 for 2025 (Form 39R Part B line 8a; 2025 Form 39R instructions p. 31).</t>
+    <t>Idaho retirement benefits deduction maximum, married filing jointly: $72,324 for 2025 (Form 39R Part B line 8a; 2025 Form 39R instructions p. 31). Line 8d is this cap less Railroad Retirement and Social Security received; line 8f is the smaller of 8d and the qualifying benefits.</t>
   </si>
   <si>
     <t>id_retirement_benefits_cap_single</t>
@@ -255,7 +264,7 @@
     <t>48216.0</t>
   </si>
   <si>
-    <t>Idaho retirement benefits deduction maximum, single: $48,216 for 2025, reduced by Social Security and Railroad Retirement benefits received (Form 39R Part B line 8a; Idaho Code 63-3022A; 2025 Form 39R instructions p. 31).</t>
+    <t>Idaho retirement benefits deduction maximum, single: $48,216 for 2025 (Form 39R Part B line 8a; Idaho Code 63-3022A; 2025 Form 39R instructions p. 31). Line 8d is this cap less Railroad Retirement (8b) and Social Security (8c) benefits received; line 8f, the deduction, is the smaller of 8d and the qualifying benefits (8e).</t>
   </si>
   <si>
     <t>id_tax_rate</t>
@@ -1821,7 +1830,7 @@
         <v>15</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="H12" s="2" t="s">
         <v>8</v>
@@ -1880,7 +1889,7 @@
         <v>18</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="H13" s="2" t="s">
         <v>8</v>
@@ -1939,7 +1948,7 @@
         <v>18</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="H14" s="2" t="s">
         <v>8</v>
@@ -1978,244 +1987,244 @@
         <v>8</v>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="1" t="s">
+    <row r="15">
+      <c r="A15" s="5">
+        <v>4</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="F15" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="G15" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H15" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="I15" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="J15" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="K15" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="L15" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="M15" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="N15" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="O15" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="P15" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q15" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="R15" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="S15" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="B16" s="1"/>
-      <c r="C16" s="1" t="s">
+      <c r="B17" s="1"/>
+      <c r="C17" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="D16" s="4">
+      <c r="D17" s="4">
         <v>1</v>
       </c>
-      <c r="E16" s="4">
+      <c r="E17" s="4">
         <v>2</v>
       </c>
-      <c r="F16" s="4">
+      <c r="F17" s="4">
         <v>3</v>
       </c>
-      <c r="G16" s="4">
+      <c r="G17" s="4">
         <v>4</v>
       </c>
-      <c r="H16" s="4">
+      <c r="H17" s="4">
         <v>5</v>
       </c>
-      <c r="I16" s="4">
+      <c r="I17" s="4">
         <v>6</v>
       </c>
-      <c r="J16" s="4">
+      <c r="J17" s="4">
         <v>7</v>
       </c>
-      <c r="K16" s="4">
-        <v>8</v>
-      </c>
-      <c r="L16" s="4">
+      <c r="K17" s="4">
+        <v>8</v>
+      </c>
+      <c r="L17" s="4">
         <v>9</v>
       </c>
-      <c r="M16" s="4">
+      <c r="M17" s="4">
         <v>10</v>
       </c>
-      <c r="N16" s="4">
+      <c r="N17" s="4">
         <v>11</v>
       </c>
-      <c r="O16" s="4">
+      <c r="O17" s="4">
         <v>12</v>
       </c>
-      <c r="P16" s="4">
+      <c r="P17" s="4">
         <v>13</v>
       </c>
-      <c r="Q16" s="4">
+      <c r="Q17" s="4">
         <v>14</v>
       </c>
-      <c r="R16" s="4">
+      <c r="R17" s="4">
         <v>15</v>
       </c>
-      <c r="S16" s="4">
+      <c r="S17" s="4">
         <v>16</v>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="5">
+    <row r="18">
+      <c r="A18" s="5">
         <v>1</v>
       </c>
-      <c r="B17" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="C17" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="D17" s="2" t="s">
+      <c r="B18" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="D18" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="E17" s="2" t="s">
+      <c r="E18" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="F17" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="G17" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="H17" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="I17" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="J17" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="K17" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="L17" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="M17" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="N17" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="O17" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="P17" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q17" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="R17" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="S17" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="1" t="s">
+      <c r="F18" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="G18" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H18" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="I18" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="J18" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="K18" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="L18" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="M18" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="N18" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="O18" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="P18" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q18" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="R18" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="S18" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="B19" s="1"/>
-      <c r="C19" s="1" t="s">
+      <c r="B20" s="1"/>
+      <c r="C20" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="D19" s="1">
+      <c r="D20" s="1">
         <v>1</v>
       </c>
-      <c r="E19" s="1">
+      <c r="E20" s="1">
         <v>2</v>
       </c>
-      <c r="F19" s="1">
+      <c r="F20" s="1">
         <v>3</v>
       </c>
-      <c r="G19" s="1">
+      <c r="G20" s="1">
         <v>4</v>
       </c>
-      <c r="H19" s="1">
+      <c r="H20" s="1">
         <v>5</v>
       </c>
-      <c r="I19" s="1">
+      <c r="I20" s="1">
         <v>6</v>
       </c>
-      <c r="J19" s="1">
+      <c r="J20" s="1">
         <v>7</v>
       </c>
-      <c r="K19" s="1">
-        <v>8</v>
-      </c>
-      <c r="L19" s="1">
+      <c r="K20" s="1">
+        <v>8</v>
+      </c>
+      <c r="L20" s="1">
         <v>9</v>
       </c>
-      <c r="M19" s="1">
+      <c r="M20" s="1">
         <v>10</v>
       </c>
-      <c r="N19" s="1">
+      <c r="N20" s="1">
         <v>11</v>
       </c>
-      <c r="O19" s="1">
+      <c r="O20" s="1">
         <v>12</v>
       </c>
-      <c r="P19" s="1">
+      <c r="P20" s="1">
         <v>13</v>
       </c>
-      <c r="Q19" s="1">
+      <c r="Q20" s="1">
         <v>14</v>
       </c>
-      <c r="R19" s="1">
+      <c r="R20" s="1">
         <v>15</v>
       </c>
-      <c r="S19" s="1">
+      <c r="S20" s="1">
         <v>16</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="5">
-        <v>1</v>
-      </c>
-      <c r="B20" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="C20" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="D20" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E20" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="F20" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="G20" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="H20" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="I20" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="J20" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="K20" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="L20" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="M20" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="N20" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="O20" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="P20" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q20" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="R20" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="S20" s="2" t="s">
-        <v>8</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C21" s="3" t="s">
         <v>8</v>
@@ -2271,60 +2280,178 @@
     </row>
     <row r="22">
       <c r="A22" s="5">
+        <v>2</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F22" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="G22" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H22" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="I22" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="J22" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="K22" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="L22" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="M22" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="N22" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="O22" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="P22" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q22" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="R22" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="S22" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="5">
         <v>3</v>
       </c>
-      <c r="B22" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="C22" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="D22" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E22" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="F22" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="G22" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="H22" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="I22" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="J22" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="K22" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="L22" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="M22" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="N22" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="O22" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="P22" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q22" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="R22" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="S22" s="2" t="s">
+      <c r="B23" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F23" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="G23" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H23" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="I23" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="J23" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="K23" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="L23" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="M23" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="N23" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="O23" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="P23" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q23" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="R23" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="S23" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="5">
+        <v>4</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F24" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="G24" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H24" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="I24" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="J24" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="K24" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="L24" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="M24" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="N24" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="O24" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="P24" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q24" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="R24" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="S24" s="2" t="s">
         <v>8</v>
       </c>
     </row>
@@ -2340,8 +2467,8 @@
     <mergeCell ref="A9:B9"/>
     <mergeCell ref="C9:S9"/>
     <mergeCell ref="A11:B11"/>
-    <mergeCell ref="A16:B16"/>
-    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="A20:B20"/>
   </mergeCells>
 </worksheet>
 </file>
@@ -2366,56 +2493,56 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="M2" s="1" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="6" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="C3" s="6"/>
       <c r="D3" s="6"/>
@@ -2434,25 +2561,25 @@
         <v>8</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="C4" s="11" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="D4" s="7" t="s">
         <v>8</v>
       </c>
       <c r="E4" s="7" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="F4" s="7" t="s">
         <v>8</v>
       </c>
       <c r="G4" s="7" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="H4" s="16" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="I4" s="7" t="s">
         <v>8</v>
@@ -2475,25 +2602,25 @@
         <v>8</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="D5" s="8" t="s">
         <v>8</v>
       </c>
       <c r="E5" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="F5" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="G5" s="8" t="s">
         <v>70</v>
       </c>
-      <c r="F5" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="G5" s="8" t="s">
-        <v>67</v>
-      </c>
       <c r="H5" s="16" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="I5" s="8" t="s">
         <v>8</v>
@@ -2516,25 +2643,25 @@
         <v>8</v>
       </c>
       <c r="B6" s="9" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="C6" s="11" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="D6" s="7" t="s">
         <v>8</v>
       </c>
       <c r="E6" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="F6" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="G6" s="7" t="s">
         <v>70</v>
       </c>
-      <c r="F6" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="G6" s="7" t="s">
-        <v>67</v>
-      </c>
       <c r="H6" s="16" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="I6" s="7" t="s">
         <v>8</v>
@@ -2557,25 +2684,25 @@
         <v>8</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="C7" s="11" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="D7" s="8" t="s">
         <v>8</v>
       </c>
       <c r="E7" s="8" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="F7" s="8" t="s">
         <v>8</v>
       </c>
       <c r="G7" s="8" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="H7" s="16" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="I7" s="8" t="s">
         <v>8</v>
@@ -2598,25 +2725,25 @@
         <v>8</v>
       </c>
       <c r="B8" s="9" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="C8" s="11" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="D8" s="7" t="s">
         <v>8</v>
       </c>
       <c r="E8" s="7" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="F8" s="7" t="s">
         <v>8</v>
       </c>
       <c r="G8" s="7" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="H8" s="16" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="I8" s="7" t="s">
         <v>8</v>
@@ -2639,25 +2766,25 @@
         <v>8</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="C9" s="11" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="D9" s="8" t="s">
         <v>8</v>
       </c>
       <c r="E9" s="8" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="F9" s="8" t="s">
         <v>8</v>
       </c>
       <c r="G9" s="8" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="H9" s="16" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="I9" s="8" t="s">
         <v>8</v>
@@ -2680,25 +2807,25 @@
         <v>8</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="C10" s="11" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="D10" s="7" t="s">
         <v>8</v>
       </c>
       <c r="E10" s="7" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="F10" s="7" t="s">
         <v>8</v>
       </c>
       <c r="G10" s="7" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="H10" s="16" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="I10" s="7" t="s">
         <v>8</v>
@@ -2721,25 +2848,25 @@
         <v>8</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="C11" s="11" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="D11" s="8" t="s">
         <v>8</v>
       </c>
       <c r="E11" s="8" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="F11" s="8" t="s">
         <v>8</v>
       </c>
       <c r="G11" s="8" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="H11" s="16" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="I11" s="8" t="s">
         <v>8</v>

--- a/sampleprojects/TaxReturn/excel/states/ID.xlsx
+++ b/sampleprojects/TaxReturn/excel/states/ID.xlsx
@@ -8,14 +8,15 @@
   </bookViews>
   <sheets>
     <sheet name="ID Tax" sheetId="2" r:id="rId4"/>
-    <sheet name="EDD" sheetId="3" r:id="rId6"/>
+    <sheet name="ID Retirement Benefits Deductio" sheetId="3" r:id="rId6"/>
+    <sheet name="EDD" sheetId="4" r:id="rId7"/>
   </sheets>
   <calcPr calcId="122211"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="92">
   <si>
     <t>DT: ID Tax</t>
   </si>
@@ -44,7 +45,7 @@
     <t/>
   </si>
   <si>
-    <t>set result.computed_state_tax = 0; set result.computed_state_taxable_income = 0; add "  Idaho Tax Calculation (top marginal 5.695%)" to job.audit_trail</t>
+    <t>set result.computed_state_tax = 0; set result.computed_state_taxable_income = 0; set result.id_military_retirement_exemption = 0.0; perform ID_Retirement_Benefits_Deduction; add "  Idaho Tax Calculation (Form 40, 2025) - 5.3% of taxable income above the zero bracket" to job.audit_trail</t>
   </si>
   <si>
     <t>CONDITIONS: COMMENTS</t>
@@ -80,25 +81,25 @@
     <t>DSL: ACTIONS</t>
   </si>
   <si>
-    <t>MFJ/QSS: $30,000 std ded, 5.695%</t>
-  </si>
-  <si>
-    <t>set result.computed_state_taxable_income = the maximum of (result.state_calc_agi - 30000.0) and 0.0; set result.computed_state_tax = result.computed_state_taxable_income * 0.05695</t>
+    <t>MFJ/QSS: Form 39R line 8d = the $72,324 cap less Social Security; 8f = the smaller of 8d and the benefits; Form 40 line 16 federal deduction; line 20 worksheet: subtract $9,622, multiply by 5.3%</t>
+  </si>
+  <si>
+    <t>set result.id_military_retirement_exemption = the minimum of result.id_military_retirement_exemption and (the maximum of (id_retirement_benefits_cap_joint - result.total_social_security) and 0.0); set result.computed_state_taxable_income = the maximum of (result.state_calc_agi - result.id_military_retirement_exemption - result.total_deduction) and 0.0; set result.computed_state_tax = (the maximum of (result.computed_state_taxable_income - id_zero_bracket_joint) and 0.0) * id_tax_rate; add "  ID Form 39R line 8 retirement benefits deduction $" + result.id_military_retirement_exemption + "; taxable income $" + result.computed_state_taxable_income + "; tax $" + result.computed_state_tax to job.audit_trail</t>
   </si>
   <si>
     <t>X</t>
   </si>
   <si>
-    <t>HOH: $22,500 std ded, 5.695%</t>
-  </si>
-  <si>
-    <t>set result.computed_state_taxable_income = the maximum of (result.state_calc_agi - 22500.0) and 0.0; set result.computed_state_tax = result.computed_state_taxable_income * 0.05695</t>
-  </si>
-  <si>
-    <t>Default (Single/MFS): $15,000 std ded, 5.695%</t>
-  </si>
-  <si>
-    <t>set result.computed_state_taxable_income = the maximum of (result.state_calc_agi - 15000.0) and 0.0; set result.computed_state_tax = result.computed_state_taxable_income * 0.05695</t>
+    <t>HOH: Form 39R line 8d = the single $48,216 cap less Social Security; 8f = the smaller of 8d and the benefits; the head-of-household zero bracket is the joint figure, $9,622; 5.3%</t>
+  </si>
+  <si>
+    <t>set result.id_military_retirement_exemption = the minimum of result.id_military_retirement_exemption and (the maximum of (id_retirement_benefits_cap_single - result.total_social_security) and 0.0); set result.computed_state_taxable_income = the maximum of (result.state_calc_agi - result.id_military_retirement_exemption - result.total_deduction) and 0.0; set result.computed_state_tax = (the maximum of (result.computed_state_taxable_income - id_zero_bracket_joint) and 0.0) * id_tax_rate; add "  ID Form 39R line 8 retirement benefits deduction $" + result.id_military_retirement_exemption + "; taxable income $" + result.computed_state_taxable_income + "; tax $" + result.computed_state_tax to job.audit_trail</t>
+  </si>
+  <si>
+    <t>Single/MFS: Form 39R line 8d = the $48,216 cap less Social Security; 8f = the smaller of 8d and the benefits; Form 40 line 16 federal deduction; line 20 worksheet: subtract $4,811, multiply by 5.3%</t>
+  </si>
+  <si>
+    <t>set result.id_military_retirement_exemption = the minimum of result.id_military_retirement_exemption and (the maximum of (id_retirement_benefits_cap_single - result.total_social_security) and 0.0); set result.computed_state_taxable_income = the maximum of (result.state_calc_agi - result.id_military_retirement_exemption - result.total_deduction) and 0.0; set result.computed_state_tax = (the maximum of (result.computed_state_taxable_income - id_zero_bracket_single) and 0.0) * id_tax_rate; add "  ID Form 39R line 8 retirement benefits deduction $" + result.id_military_retirement_exemption + "; taxable income $" + result.computed_state_taxable_income + "; tax $" + result.computed_state_tax to job.audit_trail</t>
   </si>
   <si>
     <t>Policy:</t>
@@ -107,13 +108,67 @@
     <t>Policy Statements</t>
   </si>
   <si>
-    <t>ID MFJ: 5.695% x max(AGI - $30,000, 0) per Idaho Code § 63-3024</t>
-  </si>
-  <si>
-    <t>ID HOH: 5.695% x max(AGI - $22,500, 0) per Idaho Code § 63-3024</t>
-  </si>
-  <si>
-    <t>ID Single/MFS: 5.695% x max(AGI - $15,000, 0) per Idaho Code § 63-3024</t>
+    <t>Idaho MFJ/QSS (2025 Form 40): taxable income is federal AGI less Form 39R subtractions (the retirement benefits deduction for military retired pay: line 8d = the $72,324 cap less Social Security, line 8f = the smaller of 8d and the benefits) less the federal deduction (line 16); tax is 5.3% of taxable income over the $9,622 zero bracket (line 20 worksheet; HB 40).</t>
+  </si>
+  <si>
+    <t>Idaho HOH: as MFJ, with the single $48,216 cap on Form 39R line 8a (8d = cap less Social Security; 8f = the smaller of 8d and the benefits).</t>
+  </si>
+  <si>
+    <t>Idaho Single/MFS (2025 Form 40): federal AGI less the retirement benefits deduction (Form 39R Part B line 8: 8d = the $48,216 cap less Social Security, 8f = the smaller of 8d and the benefits) less the federal deduction; 5.3% of taxable income over the $4,811 zero bracket. The refundable grocery credit and the $10 permanent building fund tax are not part of the income tax figure.</t>
+  </si>
+  <si>
+    <t>DT: ID Retirement Benefits Deduction</t>
+  </si>
+  <si>
+    <t xml:space="preserve">COMMENTS: </t>
+  </si>
+  <si>
+    <t>TABLE_NUMBER: 51613</t>
+  </si>
+  <si>
+    <t>for all taxpayers</t>
+  </si>
+  <si>
+    <t>The taxpayer has military retired pay (Form 39R Part B line 8e qualifying benefits)</t>
+  </si>
+  <si>
+    <t>taxpayer.military_retirement_pay &gt; 0</t>
+  </si>
+  <si>
+    <t>62 or older qualifies outright (Idaho Code 63-3022A(1)(b)(ii))</t>
+  </si>
+  <si>
+    <t>job.tax_year - (get yearof taxpayer.date_of_birth) &gt;= 62</t>
+  </si>
+  <si>
+    <t>Under 62: qualifies when employed during the year with enough income to have to file a federal return (63-3022A(1)(b)(iii)); wages stand in for that test</t>
+  </si>
+  <si>
+    <t>taxpayer.w2_wages &gt; 0</t>
+  </si>
+  <si>
+    <t>Full-year resident entry only. A part-year or nonresident entry's income is built from the income entities, so the pension is not in it, and 4 U.S.C. 114 bars a state from taxing a nonresident's retirement income (#1330 review).</t>
+  </si>
+  <si>
+    <t>result.state_calc_resident_status is equal to "full_year"</t>
+  </si>
+  <si>
+    <t>Form 39R Part B line 8e: qualifying retirement benefits of a retired service member; capped on line 8a-8f in ID_Tax</t>
+  </si>
+  <si>
+    <t>add taxpayer.military_retirement_pay to result.id_military_retirement_exemption</t>
+  </si>
+  <si>
+    <t>62 or older: the military retired pay is a qualifying retirement benefit for the Idaho retirement benefits deduction (Form 39R Part B line 8; Idaho Code 63-3022A; 2025 Form 39R instructions p. 31).</t>
+  </si>
+  <si>
+    <t>Under 62 and employed: the pay qualifies for the retirement benefits deduction (63-3022A(1)(b)(iii)). The disabled-at-any-age test has no input in the data model.</t>
+  </si>
+  <si>
+    <t>Under 62 and not employed, or no military retired pay: no deduction.</t>
+  </si>
+  <si>
+    <t>Not a full-year resident entry: the pension is not in this entry's sourced income (the roster builds it from the income entities) and 4 U.S.C. 114 bars taxing a nonresident's retirement income, so nothing is subtracted.</t>
   </si>
   <si>
     <t>EDD: EDD</t>
@@ -161,7 +216,7 @@
     <t>result</t>
   </si>
   <si>
-    <t>(3 attributes)</t>
+    <t>(8 attributes)</t>
   </si>
   <si>
     <t>id_military_age_requirement</t>
@@ -176,7 +231,7 @@
     <t>r</t>
   </si>
   <si>
-    <t>ID minimum age for full military retirement exemption (62)</t>
+    <t>Idaho retirement benefits deduction for retired service members: age 62 or older qualifies outright; under 62 qualifies only when employed during the year with enough earned income to have to file a federal return; disabled qualifies at any age (Idaho Code 63-3022A(1)(b); 2025 Form 39R instructions, line 8e). Military retired pay is not exempt without one of these tests.</t>
   </si>
   <si>
     <t>id_military_retirement_exemption</t>
@@ -185,13 +240,58 @@
     <t>0.0</t>
   </si>
   <si>
-    <t>ID military retirement exemption (computed - full if qualified)</t>
+    <t>Idaho retirement benefits deduction for military retired pay (computed): the qualifying pay (ID_Retirement_Benefits_Deduction, per taxpayer), capped at the filing-status maximum less Social Security received (Form 39R Part B line 8f -&gt; line 24 -&gt; Form 40 line 10) (#1330).</t>
   </si>
   <si>
     <t>id_military_retirement_taxable</t>
   </si>
   <si>
     <t>ID taxable military retirement after exemption (computed)</t>
+  </si>
+  <si>
+    <t>id_retirement_benefits_cap_joint</t>
+  </si>
+  <si>
+    <t>72324.0</t>
+  </si>
+  <si>
+    <t>Idaho retirement benefits deduction maximum, married filing jointly: $72,324 for 2025 (Form 39R Part B line 8a; 2025 Form 39R instructions p. 31). Line 8d is this cap less Railroad Retirement and Social Security received; line 8f is the smaller of 8d and the qualifying benefits.</t>
+  </si>
+  <si>
+    <t>id_retirement_benefits_cap_single</t>
+  </si>
+  <si>
+    <t>48216.0</t>
+  </si>
+  <si>
+    <t>Idaho retirement benefits deduction maximum, single: $48,216 for 2025 (Form 39R Part B line 8a; Idaho Code 63-3022A; 2025 Form 39R instructions p. 31). Line 8d is this cap less Railroad Retirement (8b) and Social Security (8c) benefits received; line 8f, the deduction, is the smaller of 8d and the qualifying benefits (8e).</t>
+  </si>
+  <si>
+    <t>id_tax_rate</t>
+  </si>
+  <si>
+    <t>0.053</t>
+  </si>
+  <si>
+    <t>Idaho individual income tax rate 5.3% effective January 1, 2025 (HB 40; 2025 Form 40 instructions, line 20 worksheet step 4). Was 5.695% for 2024.</t>
+  </si>
+  <si>
+    <t>id_zero_bracket_joint</t>
+  </si>
+  <si>
+    <t>9622.0</t>
+  </si>
+  <si>
+    <t>Idaho taxable income not taxed, married filing jointly, surviving spouse or head of household: $9,622 for 2025, twice the single figure as in prior years (2024: $4,673 single, $9,346 joint). The 2025 joint figure was not read from the Form 40 worksheet directly; confirm when a joint Idaho scenario is written.</t>
+  </si>
+  <si>
+    <t>id_zero_bracket_single</t>
+  </si>
+  <si>
+    <t>4811.0</t>
+  </si>
+  <si>
+    <t>Idaho taxable income not taxed, single or married filing separately: $4,811 for 2025 (Form 40 instructions, line 20 worksheet step 2).</t>
   </si>
 </sst>
 </file>
@@ -1479,6 +1579,904 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <dimension ref="A1"/>
   <cols>
+    <col customWidth="true" max="1" min="1" width="20"/>
+    <col customWidth="true" max="3" min="2" width="40"/>
+    <col customWidth="true" max="19" min="4" width="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="B1" s="2"/>
+      <c r="C1" s="2"/>
+      <c r="D1" s="2"/>
+      <c r="E1" s="2"/>
+      <c r="F1" s="2"/>
+      <c r="G1" s="2"/>
+      <c r="H1" s="2"/>
+      <c r="I1" s="2"/>
+      <c r="J1" s="2"/>
+      <c r="K1" s="2"/>
+      <c r="L1" s="2"/>
+      <c r="M1" s="2"/>
+      <c r="N1" s="2"/>
+      <c r="O1" s="2"/>
+      <c r="P1" s="2"/>
+      <c r="Q1" s="2"/>
+      <c r="R1" s="2"/>
+      <c r="S1" s="2"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="3"/>
+      <c r="C2" s="3"/>
+      <c r="D2" s="3"/>
+      <c r="E2" s="3"/>
+      <c r="F2" s="3"/>
+      <c r="G2" s="3"/>
+      <c r="H2" s="3"/>
+      <c r="I2" s="3"/>
+      <c r="J2" s="3"/>
+      <c r="K2" s="3"/>
+      <c r="L2" s="3"/>
+      <c r="M2" s="3"/>
+      <c r="N2" s="3"/>
+      <c r="O2" s="3"/>
+      <c r="P2" s="3"/>
+      <c r="Q2" s="3"/>
+      <c r="R2" s="3"/>
+      <c r="S2" s="3"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="B3" s="2"/>
+      <c r="C3" s="2"/>
+      <c r="D3" s="2"/>
+      <c r="E3" s="2"/>
+      <c r="F3" s="2"/>
+      <c r="G3" s="2"/>
+      <c r="H3" s="2"/>
+      <c r="I3" s="2"/>
+      <c r="J3" s="2"/>
+      <c r="K3" s="2"/>
+      <c r="L3" s="2"/>
+      <c r="M3" s="2"/>
+      <c r="N3" s="2"/>
+      <c r="O3" s="2"/>
+      <c r="P3" s="2"/>
+      <c r="Q3" s="2"/>
+      <c r="R3" s="2"/>
+      <c r="S3" s="2"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="B4" s="2"/>
+      <c r="C4" s="2"/>
+      <c r="D4" s="2"/>
+      <c r="E4" s="2"/>
+      <c r="F4" s="2"/>
+      <c r="G4" s="2"/>
+      <c r="H4" s="2"/>
+      <c r="I4" s="2"/>
+      <c r="J4" s="2"/>
+      <c r="K4" s="2"/>
+      <c r="L4" s="2"/>
+      <c r="M4" s="2"/>
+      <c r="N4" s="2"/>
+      <c r="O4" s="2"/>
+      <c r="P4" s="2"/>
+      <c r="Q4" s="2"/>
+      <c r="R4" s="2"/>
+      <c r="S4" s="2"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B6" s="1"/>
+      <c r="C6" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D6" s="1"/>
+      <c r="E6" s="1"/>
+      <c r="F6" s="1"/>
+      <c r="G6" s="1"/>
+      <c r="H6" s="1"/>
+      <c r="I6" s="1"/>
+      <c r="J6" s="1"/>
+      <c r="K6" s="1"/>
+      <c r="L6" s="1"/>
+      <c r="M6" s="1"/>
+      <c r="N6" s="1"/>
+      <c r="O6" s="1"/>
+      <c r="P6" s="1"/>
+      <c r="Q6" s="1"/>
+      <c r="R6" s="1"/>
+      <c r="S6" s="1"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="5">
+        <v>1</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="D7" s="3"/>
+      <c r="E7" s="3"/>
+      <c r="F7" s="3"/>
+      <c r="G7" s="3"/>
+      <c r="H7" s="3"/>
+      <c r="I7" s="3"/>
+      <c r="J7" s="3"/>
+      <c r="K7" s="3"/>
+      <c r="L7" s="3"/>
+      <c r="M7" s="3"/>
+      <c r="N7" s="3"/>
+      <c r="O7" s="3"/>
+      <c r="P7" s="3"/>
+      <c r="Q7" s="3"/>
+      <c r="R7" s="3"/>
+      <c r="S7" s="3"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B9" s="1"/>
+      <c r="C9" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D9" s="1"/>
+      <c r="E9" s="1"/>
+      <c r="F9" s="1"/>
+      <c r="G9" s="1"/>
+      <c r="H9" s="1"/>
+      <c r="I9" s="1"/>
+      <c r="J9" s="1"/>
+      <c r="K9" s="1"/>
+      <c r="L9" s="1"/>
+      <c r="M9" s="1"/>
+      <c r="N9" s="1"/>
+      <c r="O9" s="1"/>
+      <c r="P9" s="1"/>
+      <c r="Q9" s="1"/>
+      <c r="R9" s="1"/>
+      <c r="S9" s="1"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B11" s="1"/>
+      <c r="C11" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D11" s="1">
+        <v>1</v>
+      </c>
+      <c r="E11" s="1">
+        <v>2</v>
+      </c>
+      <c r="F11" s="1">
+        <v>3</v>
+      </c>
+      <c r="G11" s="1">
+        <v>4</v>
+      </c>
+      <c r="H11" s="1">
+        <v>5</v>
+      </c>
+      <c r="I11" s="1">
+        <v>6</v>
+      </c>
+      <c r="J11" s="1">
+        <v>7</v>
+      </c>
+      <c r="K11" s="1">
+        <v>8</v>
+      </c>
+      <c r="L11" s="1">
+        <v>9</v>
+      </c>
+      <c r="M11" s="1">
+        <v>10</v>
+      </c>
+      <c r="N11" s="1">
+        <v>11</v>
+      </c>
+      <c r="O11" s="1">
+        <v>12</v>
+      </c>
+      <c r="P11" s="1">
+        <v>13</v>
+      </c>
+      <c r="Q11" s="1">
+        <v>14</v>
+      </c>
+      <c r="R11" s="1">
+        <v>15</v>
+      </c>
+      <c r="S11" s="1">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="5">
+        <v>1</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="G12" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="I12" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="J12" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="K12" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="L12" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="M12" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="N12" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="O12" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="P12" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q12" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="R12" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="S12" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="5">
+        <v>2</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="G13" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="I13" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="J13" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="K13" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="L13" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="M13" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="N13" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="O13" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="P13" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q13" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="R13" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="S13" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="5">
+        <v>3</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="F14" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="G14" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="H14" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="I14" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="J14" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="K14" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="L14" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="M14" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="N14" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="O14" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="P14" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q14" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="R14" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="S14" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="5">
+        <v>4</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="F15" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="G15" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H15" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="I15" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="J15" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="K15" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="L15" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="M15" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="N15" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="O15" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="P15" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q15" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="R15" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="S15" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B17" s="1"/>
+      <c r="C17" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="D17" s="4">
+        <v>1</v>
+      </c>
+      <c r="E17" s="4">
+        <v>2</v>
+      </c>
+      <c r="F17" s="4">
+        <v>3</v>
+      </c>
+      <c r="G17" s="4">
+        <v>4</v>
+      </c>
+      <c r="H17" s="4">
+        <v>5</v>
+      </c>
+      <c r="I17" s="4">
+        <v>6</v>
+      </c>
+      <c r="J17" s="4">
+        <v>7</v>
+      </c>
+      <c r="K17" s="4">
+        <v>8</v>
+      </c>
+      <c r="L17" s="4">
+        <v>9</v>
+      </c>
+      <c r="M17" s="4">
+        <v>10</v>
+      </c>
+      <c r="N17" s="4">
+        <v>11</v>
+      </c>
+      <c r="O17" s="4">
+        <v>12</v>
+      </c>
+      <c r="P17" s="4">
+        <v>13</v>
+      </c>
+      <c r="Q17" s="4">
+        <v>14</v>
+      </c>
+      <c r="R17" s="4">
+        <v>15</v>
+      </c>
+      <c r="S17" s="4">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="5">
+        <v>1</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="F18" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="G18" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H18" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="I18" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="J18" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="K18" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="L18" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="M18" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="N18" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="O18" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="P18" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q18" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="R18" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="S18" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B20" s="1"/>
+      <c r="C20" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D20" s="1">
+        <v>1</v>
+      </c>
+      <c r="E20" s="1">
+        <v>2</v>
+      </c>
+      <c r="F20" s="1">
+        <v>3</v>
+      </c>
+      <c r="G20" s="1">
+        <v>4</v>
+      </c>
+      <c r="H20" s="1">
+        <v>5</v>
+      </c>
+      <c r="I20" s="1">
+        <v>6</v>
+      </c>
+      <c r="J20" s="1">
+        <v>7</v>
+      </c>
+      <c r="K20" s="1">
+        <v>8</v>
+      </c>
+      <c r="L20" s="1">
+        <v>9</v>
+      </c>
+      <c r="M20" s="1">
+        <v>10</v>
+      </c>
+      <c r="N20" s="1">
+        <v>11</v>
+      </c>
+      <c r="O20" s="1">
+        <v>12</v>
+      </c>
+      <c r="P20" s="1">
+        <v>13</v>
+      </c>
+      <c r="Q20" s="1">
+        <v>14</v>
+      </c>
+      <c r="R20" s="1">
+        <v>15</v>
+      </c>
+      <c r="S20" s="1">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="5">
+        <v>1</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F21" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="G21" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H21" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="I21" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="J21" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="K21" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="L21" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="M21" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="N21" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="O21" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="P21" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q21" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="R21" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="S21" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="5">
+        <v>2</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F22" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="G22" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H22" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="I22" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="J22" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="K22" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="L22" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="M22" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="N22" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="O22" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="P22" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q22" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="R22" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="S22" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="5">
+        <v>3</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F23" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="G23" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H23" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="I23" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="J23" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="K23" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="L23" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="M23" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="N23" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="O23" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="P23" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q23" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="R23" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="S23" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="5">
+        <v>4</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F24" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="G24" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H24" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="I24" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="J24" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="K24" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="L24" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="M24" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="N24" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="O24" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="P24" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q24" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="R24" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="S24" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="12">
+    <mergeCell ref="A1:S1"/>
+    <mergeCell ref="A2:S2"/>
+    <mergeCell ref="A3:S3"/>
+    <mergeCell ref="A4:S4"/>
+    <mergeCell ref="A6:B6"/>
+    <mergeCell ref="C6:S6"/>
+    <mergeCell ref="C7:S7"/>
+    <mergeCell ref="A9:B9"/>
+    <mergeCell ref="C9:S9"/>
+    <mergeCell ref="A11:B11"/>
+    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="A20:B20"/>
+  </mergeCells>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1"/>
+  <cols>
     <col customWidth="true" max="1" min="1" width="18"/>
     <col customWidth="true" max="2" min="2" width="25"/>
     <col customWidth="true" max="3" min="3" width="10"/>
@@ -1495,56 +2493,56 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>33</v>
+        <v>51</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
-        <v>34</v>
+        <v>52</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>35</v>
+        <v>53</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>36</v>
+        <v>54</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>37</v>
+        <v>55</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>38</v>
+        <v>56</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>39</v>
+        <v>57</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>40</v>
+        <v>58</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>41</v>
+        <v>59</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>42</v>
+        <v>60</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>43</v>
+        <v>61</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>44</v>
+        <v>62</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>45</v>
+        <v>63</v>
       </c>
       <c r="M2" s="1" t="s">
-        <v>46</v>
+        <v>64</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="6" t="s">
-        <v>47</v>
+        <v>65</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>48</v>
+        <v>66</v>
       </c>
       <c r="C3" s="6"/>
       <c r="D3" s="6"/>
@@ -1563,25 +2561,25 @@
         <v>8</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>49</v>
+        <v>67</v>
       </c>
       <c r="C4" s="11" t="s">
-        <v>50</v>
+        <v>68</v>
       </c>
       <c r="D4" s="7" t="s">
         <v>8</v>
       </c>
       <c r="E4" s="7" t="s">
-        <v>51</v>
+        <v>69</v>
       </c>
       <c r="F4" s="7" t="s">
         <v>8</v>
       </c>
       <c r="G4" s="7" t="s">
-        <v>52</v>
+        <v>70</v>
       </c>
       <c r="H4" s="16" t="s">
-        <v>53</v>
+        <v>71</v>
       </c>
       <c r="I4" s="7" t="s">
         <v>8</v>
@@ -1604,25 +2602,25 @@
         <v>8</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>54</v>
+        <v>72</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>50</v>
+        <v>68</v>
       </c>
       <c r="D5" s="8" t="s">
         <v>8</v>
       </c>
       <c r="E5" s="8" t="s">
-        <v>55</v>
+        <v>73</v>
       </c>
       <c r="F5" s="8" t="s">
         <v>8</v>
       </c>
       <c r="G5" s="8" t="s">
-        <v>52</v>
+        <v>70</v>
       </c>
       <c r="H5" s="16" t="s">
-        <v>56</v>
+        <v>74</v>
       </c>
       <c r="I5" s="8" t="s">
         <v>8</v>
@@ -1645,25 +2643,25 @@
         <v>8</v>
       </c>
       <c r="B6" s="9" t="s">
-        <v>57</v>
+        <v>75</v>
       </c>
       <c r="C6" s="11" t="s">
-        <v>50</v>
+        <v>68</v>
       </c>
       <c r="D6" s="7" t="s">
         <v>8</v>
       </c>
       <c r="E6" s="7" t="s">
-        <v>55</v>
+        <v>73</v>
       </c>
       <c r="F6" s="7" t="s">
         <v>8</v>
       </c>
       <c r="G6" s="7" t="s">
-        <v>52</v>
+        <v>70</v>
       </c>
       <c r="H6" s="16" t="s">
-        <v>58</v>
+        <v>76</v>
       </c>
       <c r="I6" s="7" t="s">
         <v>8</v>
@@ -1678,6 +2676,211 @@
         <v>8</v>
       </c>
       <c r="M6" s="7" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="B7" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="C7" s="11" t="s">
+        <v>68</v>
+      </c>
+      <c r="D7" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E7" s="8" t="s">
+        <v>78</v>
+      </c>
+      <c r="F7" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="G7" s="8" t="s">
+        <v>70</v>
+      </c>
+      <c r="H7" s="16" t="s">
+        <v>79</v>
+      </c>
+      <c r="I7" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="J7" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="K7" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="L7" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="M7" s="8" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="B8" s="9" t="s">
+        <v>80</v>
+      </c>
+      <c r="C8" s="11" t="s">
+        <v>68</v>
+      </c>
+      <c r="D8" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E8" s="7" t="s">
+        <v>81</v>
+      </c>
+      <c r="F8" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="G8" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="H8" s="16" t="s">
+        <v>82</v>
+      </c>
+      <c r="I8" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="J8" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="K8" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="L8" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="M8" s="7" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="B9" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="C9" s="11" t="s">
+        <v>68</v>
+      </c>
+      <c r="D9" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E9" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="F9" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="G9" s="8" t="s">
+        <v>70</v>
+      </c>
+      <c r="H9" s="16" t="s">
+        <v>85</v>
+      </c>
+      <c r="I9" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="J9" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="K9" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="L9" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="M9" s="8" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="B10" s="9" t="s">
+        <v>86</v>
+      </c>
+      <c r="C10" s="11" t="s">
+        <v>68</v>
+      </c>
+      <c r="D10" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E10" s="7" t="s">
+        <v>87</v>
+      </c>
+      <c r="F10" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="G10" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="H10" s="16" t="s">
+        <v>88</v>
+      </c>
+      <c r="I10" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="J10" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="K10" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="L10" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="M10" s="7" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="B11" s="9" t="s">
+        <v>89</v>
+      </c>
+      <c r="C11" s="11" t="s">
+        <v>68</v>
+      </c>
+      <c r="D11" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E11" s="8" t="s">
+        <v>90</v>
+      </c>
+      <c r="F11" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="G11" s="8" t="s">
+        <v>70</v>
+      </c>
+      <c r="H11" s="16" t="s">
+        <v>91</v>
+      </c>
+      <c r="I11" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="J11" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="K11" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="L11" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="M11" s="8" t="s">
         <v>8</v>
       </c>
     </row>
